--- a/mrp-panel-demanda/mrp-panel-demanda/data/MB51/MB51_ejemplo.xlsx
+++ b/mrp-panel-demanda/mrp-panel-demanda/data/MB51/MB51_ejemplo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="12">
   <si>
     <t>Material</t>
   </si>
@@ -385,7 +385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G353"/>
+  <dimension ref="A1:G369"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8507,6 +8507,374 @@
         <v>11</v>
       </c>
     </row>
+    <row r="354" spans="1:7">
+      <c r="A354">
+        <v>100009</v>
+      </c>
+      <c r="B354" t="s">
+        <v>7</v>
+      </c>
+      <c r="C354">
+        <v>1000</v>
+      </c>
+      <c r="D354" t="s">
+        <v>9</v>
+      </c>
+      <c r="E354" s="1">
+        <v>44927</v>
+      </c>
+      <c r="F354">
+        <v>31</v>
+      </c>
+      <c r="G354" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7">
+      <c r="A355">
+        <v>100009</v>
+      </c>
+      <c r="B355" t="s">
+        <v>7</v>
+      </c>
+      <c r="C355">
+        <v>1000</v>
+      </c>
+      <c r="D355" t="s">
+        <v>10</v>
+      </c>
+      <c r="E355" s="1">
+        <v>45047</v>
+      </c>
+      <c r="F355">
+        <v>-12</v>
+      </c>
+      <c r="G355" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7">
+      <c r="A356">
+        <v>100009</v>
+      </c>
+      <c r="B356" t="s">
+        <v>7</v>
+      </c>
+      <c r="C356">
+        <v>1000</v>
+      </c>
+      <c r="D356" t="s">
+        <v>9</v>
+      </c>
+      <c r="E356" s="1">
+        <v>45086</v>
+      </c>
+      <c r="F356">
+        <v>76</v>
+      </c>
+      <c r="G356" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7">
+      <c r="A357">
+        <v>100009</v>
+      </c>
+      <c r="B357" t="s">
+        <v>7</v>
+      </c>
+      <c r="C357">
+        <v>1000</v>
+      </c>
+      <c r="D357" t="s">
+        <v>9</v>
+      </c>
+      <c r="E357" s="1">
+        <v>45155</v>
+      </c>
+      <c r="F357">
+        <v>28</v>
+      </c>
+      <c r="G357" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7">
+      <c r="A358">
+        <v>100009</v>
+      </c>
+      <c r="B358" t="s">
+        <v>7</v>
+      </c>
+      <c r="C358">
+        <v>1000</v>
+      </c>
+      <c r="D358" t="s">
+        <v>9</v>
+      </c>
+      <c r="E358" s="1">
+        <v>45249</v>
+      </c>
+      <c r="F358">
+        <v>62</v>
+      </c>
+      <c r="G358" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7">
+      <c r="A359">
+        <v>100009</v>
+      </c>
+      <c r="B359" t="s">
+        <v>7</v>
+      </c>
+      <c r="C359">
+        <v>1000</v>
+      </c>
+      <c r="D359" t="s">
+        <v>9</v>
+      </c>
+      <c r="E359" s="1">
+        <v>45281</v>
+      </c>
+      <c r="F359">
+        <v>69</v>
+      </c>
+      <c r="G359" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7">
+      <c r="A360">
+        <v>100009</v>
+      </c>
+      <c r="B360" t="s">
+        <v>7</v>
+      </c>
+      <c r="C360">
+        <v>1000</v>
+      </c>
+      <c r="D360" t="s">
+        <v>10</v>
+      </c>
+      <c r="E360" s="1">
+        <v>45417</v>
+      </c>
+      <c r="F360">
+        <v>-29</v>
+      </c>
+      <c r="G360" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7">
+      <c r="A361">
+        <v>100009</v>
+      </c>
+      <c r="B361" t="s">
+        <v>7</v>
+      </c>
+      <c r="C361">
+        <v>1000</v>
+      </c>
+      <c r="D361" t="s">
+        <v>9</v>
+      </c>
+      <c r="E361" s="1">
+        <v>45536</v>
+      </c>
+      <c r="F361">
+        <v>61</v>
+      </c>
+      <c r="G361" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7">
+      <c r="A362">
+        <v>100009</v>
+      </c>
+      <c r="B362" t="s">
+        <v>7</v>
+      </c>
+      <c r="C362">
+        <v>1000</v>
+      </c>
+      <c r="D362" t="s">
+        <v>9</v>
+      </c>
+      <c r="E362" s="1">
+        <v>45600</v>
+      </c>
+      <c r="F362">
+        <v>63</v>
+      </c>
+      <c r="G362" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7">
+      <c r="A363">
+        <v>100009</v>
+      </c>
+      <c r="B363" t="s">
+        <v>7</v>
+      </c>
+      <c r="C363">
+        <v>1000</v>
+      </c>
+      <c r="D363" t="s">
+        <v>9</v>
+      </c>
+      <c r="E363" s="1">
+        <v>45690</v>
+      </c>
+      <c r="F363">
+        <v>42</v>
+      </c>
+      <c r="G363" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7">
+      <c r="A364">
+        <v>100009</v>
+      </c>
+      <c r="B364" t="s">
+        <v>7</v>
+      </c>
+      <c r="C364">
+        <v>1000</v>
+      </c>
+      <c r="D364" t="s">
+        <v>9</v>
+      </c>
+      <c r="E364" s="1">
+        <v>45738</v>
+      </c>
+      <c r="F364">
+        <v>60</v>
+      </c>
+      <c r="G364" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7">
+      <c r="A365">
+        <v>100009</v>
+      </c>
+      <c r="B365" t="s">
+        <v>7</v>
+      </c>
+      <c r="C365">
+        <v>1000</v>
+      </c>
+      <c r="D365" t="s">
+        <v>9</v>
+      </c>
+      <c r="E365" s="1">
+        <v>45876</v>
+      </c>
+      <c r="F365">
+        <v>34</v>
+      </c>
+      <c r="G365" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7">
+      <c r="A366">
+        <v>100009</v>
+      </c>
+      <c r="B366" t="s">
+        <v>7</v>
+      </c>
+      <c r="C366">
+        <v>1000</v>
+      </c>
+      <c r="D366" t="s">
+        <v>9</v>
+      </c>
+      <c r="E366" s="1">
+        <v>46012</v>
+      </c>
+      <c r="F366">
+        <v>64</v>
+      </c>
+      <c r="G366" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367">
+        <v>100009</v>
+      </c>
+      <c r="B367" t="s">
+        <v>7</v>
+      </c>
+      <c r="C367">
+        <v>1000</v>
+      </c>
+      <c r="D367" t="s">
+        <v>9</v>
+      </c>
+      <c r="E367" s="1">
+        <v>46067</v>
+      </c>
+      <c r="F367">
+        <v>39</v>
+      </c>
+      <c r="G367" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7">
+      <c r="A368">
+        <v>100009</v>
+      </c>
+      <c r="B368" t="s">
+        <v>7</v>
+      </c>
+      <c r="C368">
+        <v>1000</v>
+      </c>
+      <c r="D368" t="s">
+        <v>9</v>
+      </c>
+      <c r="E368" s="1">
+        <v>46126</v>
+      </c>
+      <c r="F368">
+        <v>29</v>
+      </c>
+      <c r="G368" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7">
+      <c r="A369">
+        <v>100009</v>
+      </c>
+      <c r="B369" t="s">
+        <v>7</v>
+      </c>
+      <c r="C369">
+        <v>1000</v>
+      </c>
+      <c r="D369" t="s">
+        <v>9</v>
+      </c>
+      <c r="E369" s="1">
+        <v>46154</v>
+      </c>
+      <c r="F369">
+        <v>33</v>
+      </c>
+      <c r="G369" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
